--- a/data/input_data.xlsx
+++ b/data/input_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\PycharmProjects\EnergyProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB7FC62-35B9-4FC5-B0FC-7CDA4C8CE6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0354D64-5826-4272-8AF2-4FCEF4E52D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="134">
   <si>
     <t xml:space="preserve">Installed capacity </t>
   </si>
@@ -529,6 +529,26 @@
   </si>
   <si>
     <t>Winter-20</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>a*b=ac</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>wind</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>coal</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>gas</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>grid</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1002,7 +1022,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1217,6 +1237,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3178,7 +3201,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:L1001"/>
+  <dimension ref="A1:L1001"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.6328125" customWidth="1"/>
@@ -3196,19 +3219,24 @@
     <col min="13" max="27" width="7.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" customHeight="1">
+    <row r="1" spans="1:12" ht="15" customHeight="1">
       <c r="B1" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="2:12" ht="18" customHeight="1">
+      <c r="C1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="18" customHeight="1">
       <c r="B2" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -3218,7 +3246,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="2:12" ht="18" customHeight="1">
+    <row r="3" spans="1:12" ht="18" customHeight="1">
       <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
@@ -3251,7 +3279,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="14.4" customHeight="1">
+    <row r="4" spans="1:12" ht="14.4" customHeight="1">
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
         <v>41</v>
@@ -3282,7 +3310,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="18" customHeight="1">
+    <row r="5" spans="1:12" ht="18" customHeight="1">
       <c r="B5" s="22" t="s">
         <v>37</v>
       </c>
@@ -3315,7 +3343,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="18" customHeight="1">
+    <row r="6" spans="1:12" ht="18" customHeight="1">
+      <c r="A6">
+        <v>100</v>
+      </c>
       <c r="B6" s="25" t="s">
         <v>4</v>
       </c>
@@ -3348,12 +3379,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18" customHeight="1">
+    <row r="7" spans="1:12" ht="18" customHeight="1">
+      <c r="A7">
+        <v>35</v>
+      </c>
       <c r="B7" s="23" t="s">
         <v>101</v>
       </c>
       <c r="C7" s="58">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D7" s="35">
         <v>0.35</v>
@@ -3373,30 +3407,33 @@
       </c>
       <c r="I7" s="3">
         <f>C7*D7</f>
-        <v>10.5</v>
+        <v>35</v>
       </c>
       <c r="J7" s="12">
         <f>+C7*D7*E7</f>
-        <v>91980</v>
+        <v>306600</v>
       </c>
       <c r="K7" s="12">
         <f>+J7*(F7+G7)</f>
-        <v>7358400</v>
+        <v>24528000</v>
       </c>
       <c r="L7" s="11">
         <f>+H7*J7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18" customHeight="1">
+    <row r="8" spans="1:12" ht="18" customHeight="1">
+      <c r="A8">
+        <v>65</v>
+      </c>
       <c r="B8" s="24" t="s">
         <v>75</v>
       </c>
       <c r="C8" s="59">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D8" s="36">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E8" s="10">
         <f>24*365</f>
@@ -3416,26 +3453,26 @@
       </c>
       <c r="J8" s="12">
         <f t="shared" ref="J8:J15" si="0">+C8*D8*E8</f>
-        <v>315360</v>
+        <v>876000</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" ref="K8:K15" si="1">+J8*(F8+G8)</f>
-        <v>31536000</v>
+        <v>87600000</v>
       </c>
       <c r="L8" s="12">
         <f t="shared" ref="L8:L15" si="2">+H8*J8</f>
-        <v>110376</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18" customHeight="1">
+        <v>306600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="18" customHeight="1">
       <c r="B9" s="24" t="s">
         <v>76</v>
       </c>
       <c r="C9" s="59">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D9" s="36">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E9" s="10">
         <f t="shared" ref="E9:E11" si="3">24*365</f>
@@ -3452,22 +3489,22 @@
       </c>
       <c r="I9" s="3">
         <f t="shared" ref="I9:I12" si="4">C9*D9</f>
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>236520</v>
+        <v>87600</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>16556400</v>
+        <v>6132000</v>
       </c>
       <c r="L9" s="12">
         <f t="shared" si="2"/>
-        <v>201042</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18" customHeight="1">
+        <v>74460</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18" customHeight="1">
       <c r="B10" s="24" t="s">
         <v>77</v>
       </c>
@@ -3475,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="36">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="3"/>
@@ -3507,15 +3544,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="18" customHeight="1">
+    <row r="11" spans="1:12" ht="18" customHeight="1">
       <c r="B11" s="24" t="s">
         <v>78</v>
       </c>
       <c r="C11" s="59">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D11" s="36">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="3"/>
@@ -3532,30 +3569,30 @@
       </c>
       <c r="I11" s="3">
         <f t="shared" si="4"/>
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>210240</v>
+        <v>87600</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>42048000</v>
+        <v>17520000</v>
       </c>
       <c r="L11" s="12">
         <f t="shared" si="2"/>
-        <v>21024</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18" customHeight="1">
+        <v>8760</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="18" customHeight="1">
       <c r="B12" s="25" t="s">
         <v>104</v>
       </c>
       <c r="C12" s="59">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D12" s="36">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" s="10">
         <f>24*365</f>
@@ -3572,22 +3609,22 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J12" s="12">
         <f t="shared" ref="J12" si="5">+C12*D12*E12</f>
-        <v>140160</v>
+        <v>87600</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" ref="K12" si="6">+J12*(F12+G12)</f>
-        <v>49056000</v>
+        <v>30660000</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" ref="L12" si="7">+H12*J12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="18" customHeight="1">
+    <row r="13" spans="1:12" ht="18" customHeight="1">
       <c r="B13" s="11"/>
       <c r="C13" s="54"/>
       <c r="D13" s="11"/>
@@ -3609,8 +3646,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="18" customHeight="1">
-      <c r="B14" s="26"/>
+    <row r="14" spans="1:12" ht="18" customHeight="1">
+      <c r="B14" s="72"/>
       <c r="C14" s="55"/>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
@@ -3630,7 +3667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="18" customHeight="1">
+    <row r="15" spans="1:12" ht="18" customHeight="1">
       <c r="B15" s="26"/>
       <c r="C15" s="55"/>
       <c r="D15" s="26"/>
@@ -3651,11 +3688,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="18" customHeight="1">
+    <row r="16" spans="1:12" ht="18" customHeight="1">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="D16" s="3">
+        <v>70</v>
+      </c>
+      <c r="E16" s="3">
+        <v>30</v>
+      </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -3670,7 +3711,7 @@
       </c>
       <c r="C17" s="47">
         <f>SUM(C7:C15)</f>
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="D17" s="47"/>
       <c r="E17" s="47"/>
@@ -3680,15 +3721,15 @@
       <c r="I17" s="47"/>
       <c r="J17" s="60">
         <f t="shared" ref="J17:L17" si="8">SUM(J7:J15)</f>
-        <v>994260</v>
+        <v>1445400</v>
       </c>
       <c r="K17" s="60">
         <f t="shared" si="8"/>
-        <v>146554800</v>
+        <v>166440000</v>
       </c>
       <c r="L17" s="60">
         <f t="shared" si="8"/>
-        <v>332442</v>
+        <v>389820</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="18" customHeight="1">
@@ -3705,11 +3746,11 @@
       <c r="J18" s="3"/>
       <c r="K18" s="69">
         <f>+K17/J17</f>
-        <v>147.40088105726872</v>
+        <v>115.15151515151516</v>
       </c>
       <c r="L18" s="64">
         <f>+L17/J17</f>
-        <v>0.33436123348017621</v>
+        <v>0.26969696969696971</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="18" customHeight="1">
@@ -3737,7 +3778,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3">
         <f>+J17/J19</f>
-        <v>113.5</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="18" customHeight="1">
@@ -3745,16 +3786,57 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="F21" s="3">
+        <v>100</v>
+      </c>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="3">
+        <v>30</v>
+      </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:12" ht="18" customHeight="1"/>
-    <row r="23" spans="2:12" ht="18" customHeight="1"/>
-    <row r="24" spans="2:12" ht="18" customHeight="1"/>
-    <row r="25" spans="2:12" ht="18" customHeight="1"/>
+    <row r="22" spans="2:12" ht="18" customHeight="1">
+      <c r="E22" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22">
+        <v>30</v>
+      </c>
+      <c r="G22">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18" customHeight="1">
+      <c r="E23" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23">
+        <v>40</v>
+      </c>
+      <c r="G23">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18" customHeight="1">
+      <c r="E24" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24">
+        <v>40</v>
+      </c>
+      <c r="G24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="18" customHeight="1">
+      <c r="E25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25">
+        <v>90</v>
+      </c>
+    </row>
     <row r="26" spans="2:12" ht="18" customHeight="1"/>
     <row r="27" spans="2:12" ht="18" customHeight="1"/>
     <row r="28" spans="2:12" ht="18" customHeight="1"/>
@@ -4734,7 +4816,7 @@
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4819,32 +4901,32 @@
       </c>
       <c r="C7" s="61">
         <f>+'onsite-power'!J17</f>
-        <v>994260</v>
+        <v>1445400</v>
       </c>
       <c r="D7" s="61">
         <f>+'onsite-power'!K17</f>
-        <v>146554800</v>
+        <v>166440000</v>
       </c>
       <c r="E7" s="61">
         <f>+'onsite-power'!L17</f>
-        <v>332442</v>
+        <v>389820</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="8">
         <f>+D7/C7</f>
-        <v>147.40088105726872</v>
+        <v>115.15151515151516</v>
       </c>
       <c r="H7" s="64">
         <f>+E7/C7</f>
-        <v>0.33436123348017621</v>
+        <v>0.26969696969696971</v>
       </c>
       <c r="J7" s="8">
         <f>+H7*B17</f>
-        <v>66.872246696035248</v>
+        <v>53.939393939393945</v>
       </c>
       <c r="K7" s="45">
         <f>+J7+G7</f>
-        <v>214.27312775330398</v>
+        <v>169.09090909090909</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4898,15 +4980,15 @@
       </c>
       <c r="C10" s="48">
         <f>SUM(C7:C8)</f>
-        <v>1264260</v>
+        <v>1715400</v>
       </c>
       <c r="D10" s="48">
         <f t="shared" ref="D10:E10" si="0">SUM(D7:D8)</f>
-        <v>170584800</v>
+        <v>190470000</v>
       </c>
       <c r="E10" s="48">
         <f t="shared" si="0"/>
-        <v>419865.75</v>
+        <v>477243.75</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -4936,7 +5018,7 @@
       <c r="A13" s="3"/>
       <c r="C13" s="8">
         <f>+C10/C12</f>
-        <v>144.32191780821918</v>
+        <v>195.82191780821918</v>
       </c>
       <c r="D13" s="3">
         <f>100</f>
@@ -5007,7 +5089,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="12">
         <f>+B17*E10</f>
-        <v>83973150</v>
+        <v>95448750</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -5020,7 +5102,7 @@
       </c>
       <c r="E21" s="63">
         <f>+E19+D10</f>
-        <v>254557950</v>
+        <v>285918750</v>
       </c>
     </row>
     <row r="22" spans="1:7">
